--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="176">
   <si>
     <t>Term</t>
   </si>
@@ -517,7 +517,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:29:00</t>
+    <t>22:57:57</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Default Department</t>
   </si>
   <si>
     <t>Version</t>
@@ -3263,7 +3266,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3350,6 +3353,14 @@
         <v>32</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -76,10 +76,10 @@
     <t>FA</t>
   </si>
   <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>380</t>
+    <t>AMUS</t>
+  </si>
+  <si>
+    <t>112</t>
   </si>
   <si>
     <t>A</t>
@@ -88,169 +88,169 @@
     <t>4</t>
   </si>
   <si>
+    <t>MWF</t>
+  </si>
+  <si>
+    <t>09:15:00 - 10:20:00</t>
+  </si>
+  <si>
+    <t>NH 101</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>FA-Full</t>
+  </si>
+  <si>
+    <t>Musical Patterns I</t>
+  </si>
+  <si>
+    <t>Ada Example</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
+  </si>
+  <si>
+    <t>Ada Example is booked in two rooms at once</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>SP-Full</t>
+  </si>
+  <si>
+    <t>Musical Patterns I (second semester)</t>
+  </si>
+  <si>
+    <t>Different term: no conflict with the fall courses</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>10:30:00 - 11:35:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>10:30 is not a standard start time on MWF</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
     <t>TR</t>
   </si>
   <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>Same room as BHAV 212: a room conflict</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>Ben Sample</t>
+  </si>
+  <si>
+    <t>Overlaps Ben Sample's other course for part of the time (and 15:05 is not a standard start for 100 minutes)</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 106</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>Eli Specimen</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>Co-taught: Dee Placeholder is also in BHAV 112 at this time</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
     <t>15:05:00 - 16:45:00</t>
   </si>
   <si>
     <t>SB 110</t>
   </si>
   <si>
-    <t>Full</t>
-  </si>
-  <si>
-    <t>FA-Full</t>
-  </si>
-  <si>
-    <t>Data Ethics</t>
-  </si>
-  <si>
-    <t>Ben Sample</t>
-  </si>
-  <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>MWF</t>
-  </si>
-  <si>
-    <t>09:15:00 - 10:20:00</t>
-  </si>
-  <si>
-    <t>NH 101</t>
-  </si>
-  <si>
-    <t>Calculus I</t>
-  </si>
-  <si>
-    <t>Ada Example</t>
-  </si>
-  <si>
-    <t>Ada Example is booked in two rooms at once</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>SP-Full</t>
-  </si>
-  <si>
-    <t>Calculus I (second semester)</t>
-  </si>
-  <si>
-    <t>Different term: no conflict with the fall courses</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Linear Algebra</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Same room as STAT 243: a room conflict</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>10:30:00 - 11:35:00</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Discrete Mathematics</t>
-  </si>
-  <si>
-    <t>10:30 is not a standard start time on MWF</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Real Analysis I</t>
-  </si>
-  <si>
-    <t>Overlaps Ben Sample's other course for part of the time (and 15:05 is not a standard start for 100 minutes)</t>
-  </si>
-  <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>NH 106</t>
-  </si>
-  <si>
-    <t>Introduction to Statistics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>Statistical Methods</t>
-  </si>
-  <si>
-    <t>Eli Specimen</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
-    <t>Co-taught: Dee Placeholder is also in STAT 143 at this time</t>
+    <t>Information Ethics</t>
   </si>
   <si>
     <t>SectionId</t>
@@ -289,7 +289,7 @@
     <t>EnrollmentDay10</t>
   </si>
   <si>
-    <t>AY25-FA-MATH143-A</t>
+    <t>AY25-FA-AMUS112-A</t>
   </si>
   <si>
     <t>AY25</t>
@@ -298,49 +298,49 @@
     <t>09:15</t>
   </si>
   <si>
-    <t>AY25-FA-MATH143-B</t>
-  </si>
-  <si>
-    <t>AY25-FA-MATH231-A</t>
+    <t>AY25-FA-AMUS112-B</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS228-A</t>
   </si>
   <si>
     <t>10:20</t>
   </si>
   <si>
-    <t>AY25-FA-STAT243-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-MATH256-A</t>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS203-A</t>
   </si>
   <si>
     <t>10:30</t>
   </si>
   <si>
-    <t>AY25-FA-MATH351-A</t>
+    <t>AY25-FA-AMUS368-A</t>
   </si>
   <si>
     <t>14:10</t>
   </si>
   <si>
-    <t>AY25-FA-DATA380-A</t>
+    <t>AY25-FA-DIGI371-A</t>
   </si>
   <si>
     <t>15:05</t>
   </si>
   <si>
-    <t>AY25-FA-STAT343-A</t>
+    <t>AY25-FA-BHAV312-A</t>
   </si>
   <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>AY25-FA-STAT143-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH144-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT244-A</t>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
   </si>
   <si>
     <t>Activity</t>
@@ -397,22 +397,22 @@
     <t>Meets</t>
   </si>
   <si>
-    <t>Math major, year 2</t>
+    <t>AMUS major, year 2</t>
   </si>
   <si>
     <t>takeable</t>
   </si>
   <si>
-    <t>MATH 231</t>
-  </si>
-  <si>
-    <t>A student in this cohort should be able to take all three courses. MATH 231 and STAT 243 each have one section and meet at the same time</t>
-  </si>
-  <si>
-    <t>STAT 243</t>
-  </si>
-  <si>
-    <t>MATH 256</t>
+    <t>AMUS 228</t>
+  </si>
+  <si>
+    <t>A student in this cohort should be able to take all three courses. AMUS 228 and BHAV 212 each have one section and meet at the same time</t>
+  </si>
+  <si>
+    <t>BHAV 212</t>
+  </si>
+  <si>
+    <t>AMUS 203</t>
   </si>
   <si>
     <t>Kind</t>
@@ -511,13 +511,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-03</t>
+    <t>2026-10-04</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>22:57:57</t>
+    <t>08:26:04</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -938,7 +938,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="13" max="13" width="38" customWidth="1"/>
     <col min="14" max="14" width="31" customWidth="1"/>
     <col min="15" max="15" width="21" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -1037,7 +1037,7 @@
         <v>27</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M2" t="s">
         <v>28</v>
@@ -1055,7 +1055,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1063,13 +1063,13 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
@@ -1078,13 +1078,13 @@
         <v>22</v>
       </c>
       <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
         <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
       </c>
       <c r="J3" t="s">
         <v>26</v>
@@ -1096,10 +1096,10 @@
         <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s">
         <v>30</v>
@@ -1108,24 +1108,24 @@
         <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
@@ -1134,28 +1134,28 @@
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
         <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L4">
         <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="O4" t="s">
         <v>30</v>
@@ -1164,21 +1164,21 @@
         <v>31</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -1190,28 +1190,28 @@
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
         <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="L5">
         <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
         <v>30</v>
@@ -1220,10 +1220,10 @@
         <v>31</v>
       </c>
       <c r="Q5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1231,10 +1231,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
@@ -1246,7 +1246,7 @@
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
         <v>49</v>
@@ -1267,7 +1267,7 @@
         <v>51</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
         <v>30</v>
@@ -1276,10 +1276,10 @@
         <v>31</v>
       </c>
       <c r="Q6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1287,10 +1287,10 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
@@ -1302,13 +1302,13 @@
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" t="s">
         <v>55</v>
-      </c>
-      <c r="I7" t="s">
-        <v>56</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
@@ -1317,13 +1317,13 @@
         <v>27</v>
       </c>
       <c r="L7">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s">
         <v>57</v>
-      </c>
-      <c r="N7" t="s">
-        <v>52</v>
       </c>
       <c r="O7" t="s">
         <v>30</v>
@@ -1335,7 +1335,7 @@
         <v>58</v>
       </c>
       <c r="R7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1343,10 +1343,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
@@ -1373,13 +1373,13 @@
         <v>27</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M8" t="s">
         <v>62</v>
       </c>
       <c r="N8" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="O8" t="s">
         <v>30</v>
@@ -1388,10 +1388,10 @@
         <v>31</v>
       </c>
       <c r="Q8" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="R8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1399,10 +1399,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
         <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
@@ -1414,13 +1414,13 @@
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
@@ -1429,13 +1429,13 @@
         <v>27</v>
       </c>
       <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9" t="s">
         <v>65</v>
       </c>
-      <c r="M9" t="s">
-        <v>67</v>
-      </c>
       <c r="N9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O9" t="s">
         <v>30</v>
@@ -1444,21 +1444,21 @@
         <v>31</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -1470,7 +1470,7 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
         <v>49</v>
@@ -1482,16 +1482,16 @@
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O10" t="s">
         <v>30</v>
@@ -1500,21 +1500,21 @@
         <v>31</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
@@ -1529,22 +1529,22 @@
         <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
         <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N11" t="s">
         <v>71</v>
@@ -1556,10 +1556,10 @@
         <v>31</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="R11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1567,7 +1567,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
         <v>74</v>
@@ -1582,13 +1582,13 @@
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="J12" t="s">
         <v>26</v>
@@ -1597,13 +1597,13 @@
         <v>27</v>
       </c>
       <c r="L12">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N12" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="O12" t="s">
         <v>30</v>
@@ -1612,10 +1612,10 @@
         <v>31</v>
       </c>
       <c r="Q12" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="R12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1643,7 +1643,7 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
@@ -1732,7 +1732,7 @@
         <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>91</v>
@@ -1744,16 +1744,16 @@
         <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1762,10 +1762,10 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
         <v>92</v>
@@ -1774,31 +1774,31 @@
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="R2" t="s">
         <v>30</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U2" t="s">
         <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="W2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -1806,7 +1806,7 @@
         <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -1818,16 +1818,16 @@
         <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1836,10 +1836,10 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N3" t="s">
         <v>92</v>
@@ -1848,31 +1848,31 @@
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
         <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U3" t="s">
         <v>31</v>
       </c>
       <c r="V3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -1880,7 +1880,7 @@
         <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>91</v>
@@ -1892,16 +1892,16 @@
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1910,10 +1910,10 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N4" t="s">
         <v>95</v>
@@ -1931,22 +1931,22 @@
         <v>30</v>
       </c>
       <c r="S4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U4" t="s">
         <v>31</v>
       </c>
       <c r="V4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -1954,7 +1954,7 @@
         <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
         <v>91</v>
@@ -1966,16 +1966,16 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
         <v>64</v>
-      </c>
-      <c r="G5" t="s">
-        <v>69</v>
       </c>
       <c r="H5" t="s">
         <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1984,10 +1984,10 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N5" t="s">
         <v>95</v>
@@ -1999,28 +1999,28 @@
         <v>50</v>
       </c>
       <c r="Q5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U5" t="s">
         <v>31</v>
       </c>
       <c r="V5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -2028,7 +2028,7 @@
         <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>91</v>
@@ -2040,16 +2040,16 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
         <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -2058,10 +2058,10 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
         <v>98</v>
@@ -2070,31 +2070,31 @@
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="Q6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U6" t="s">
         <v>31</v>
       </c>
       <c r="V6" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="W6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -2102,7 +2102,7 @@
         <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>91</v>
@@ -2114,16 +2114,16 @@
         <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
         <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2132,10 +2132,10 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N7" t="s">
         <v>100</v>
@@ -2144,31 +2144,31 @@
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U7" t="s">
         <v>31</v>
       </c>
       <c r="V7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="W7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>91</v>
@@ -2188,16 +2188,16 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2206,10 +2206,10 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N8" t="s">
         <v>102</v>
@@ -2218,31 +2218,31 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="R8" t="s">
         <v>30</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U8" t="s">
         <v>31</v>
       </c>
       <c r="V8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -2250,7 +2250,7 @@
         <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
@@ -2262,16 +2262,16 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
         <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2280,10 +2280,10 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N9" t="s">
         <v>104</v>
@@ -2292,31 +2292,31 @@
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U9" t="s">
         <v>31</v>
       </c>
       <c r="V9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="W9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -2324,7 +2324,7 @@
         <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>91</v>
@@ -2336,16 +2336,16 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
         <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -2354,10 +2354,10 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N10" t="s">
         <v>104</v>
@@ -2366,31 +2366,31 @@
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="R10" t="s">
         <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U10" t="s">
         <v>31</v>
       </c>
       <c r="V10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -2398,28 +2398,28 @@
         <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s">
         <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2428,10 +2428,10 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N11" t="s">
         <v>92</v>
@@ -2440,31 +2440,31 @@
         <v>65</v>
       </c>
       <c r="P11" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="Q11" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U11" t="s">
         <v>31</v>
       </c>
       <c r="V11" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="W11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -2472,28 +2472,28 @@
         <v>107</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
         <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -2502,10 +2502,10 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N12" t="s">
         <v>95</v>
@@ -2517,28 +2517,28 @@
         <v>50</v>
       </c>
       <c r="Q12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U12" t="s">
         <v>31</v>
       </c>
       <c r="V12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2706,52 +2706,52 @@
         <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T2" t="s">
         <v>129</v>
@@ -2768,55 +2768,55 @@
         <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2830,55 +2830,55 @@
         <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2926,16 +2926,16 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,19 +2943,19 @@
         <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2966,16 +2966,16 @@
         <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2986,16 +2986,16 @@
         <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3006,16 +3006,16 @@
         <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3029,13 +3029,13 @@
         <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3049,13 +3049,13 @@
         <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,19 +3063,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
         <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3089,13 +3089,13 @@
         <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3109,7 +3109,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3129,7 +3129,7 @@
         <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3149,7 +3149,7 @@
         <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -3169,7 +3169,7 @@
         <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3183,13 +3183,13 @@
         <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
         <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -3209,7 +3209,7 @@
         <v>157</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -3229,7 +3229,7 @@
         <v>159</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -3310,7 +3310,7 @@
         <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3318,7 +3318,7 @@
         <v>168</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3342,7 +3342,7 @@
         <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3350,7 +3350,7 @@
         <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3358,7 +3358,7 @@
         <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -517,7 +517,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:26:04</t>
+    <t>08:32:09</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -517,7 +517,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:32:09</t>
+    <t>21:03:16</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="180">
   <si>
     <t>Term</t>
   </si>
@@ -73,6 +73,15 @@
     <t>CrossListings</t>
   </si>
   <si>
+    <t>CoreTag</t>
+  </si>
+  <si>
+    <t>SpecialTopic</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -121,6 +130,9 @@
     <t/>
   </si>
   <si>
+    <t>UGRAD</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -511,13 +523,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-04</t>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>21:03:16</t>
+    <t>13:27:37</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -925,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -944,9 +956,11 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1001,621 +1015,729 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2">
         <v>65</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="K3" t="s">
         <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
       </c>
       <c r="L3">
         <v>65</v>
       </c>
       <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="N3" t="s">
+      <c r="J4" t="s">
         <v>29</v>
       </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L4">
         <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
         <v>29</v>
       </c>
-      <c r="O4" t="s">
+      <c r="K5" t="s">
         <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
       </c>
       <c r="L5">
         <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R5" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
         <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>46</v>
-      </c>
-      <c r="R5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
         <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="s">
         <v>30</v>
-      </c>
-      <c r="P7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>58</v>
-      </c>
-      <c r="R7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
       </c>
       <c r="L8">
         <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N8" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>63</v>
       </c>
-      <c r="O8" t="s">
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
         <v>30</v>
-      </c>
-      <c r="P8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" t="s">
         <v>30</v>
-      </c>
-      <c r="P10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
-        <v>27</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O11" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" t="s">
         <v>30</v>
-      </c>
-      <c r="P11" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>72</v>
-      </c>
-      <c r="R11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" t="s">
+        <v>36</v>
+      </c>
+      <c r="U12" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1651,17 +1773,18 @@
     <col min="22" max="22" width="40" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1685,22 +1808,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -1709,10 +1832,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -1721,39 +1844,45 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1762,72 +1891,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
         <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1836,72 +1971,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1910,72 +2051,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1984,72 +2131,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -2058,72 +2211,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="W6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2132,72 +2291,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="R7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="W7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2206,72 +2371,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="R8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2280,72 +2451,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="W9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -2354,72 +2531,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="O10">
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="R10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2428,72 +2611,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O11">
         <v>65</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V11" t="s">
+        <v>44</v>
+      </c>
+      <c r="W11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="W11" t="s">
-        <v>33</v>
-      </c>
-      <c r="X11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -2502,43 +2691,49 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X12" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2754,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2586,19 +2781,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -2635,61 +2830,61 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -2697,188 +2892,188 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2900,122 +3095,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,19 +3218,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,19 +3258,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,33 +3278,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3120,16 +3315,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3140,16 +3335,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -3160,16 +3355,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3180,16 +3375,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -3200,16 +3395,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -3220,16 +3415,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -3240,16 +3435,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3275,90 +3470,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="184">
   <si>
     <t>Term</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Colocations</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -409,6 +412,15 @@
     <t>Meets</t>
   </si>
   <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>AMUS major, year 2</t>
   </si>
   <si>
@@ -418,6 +430,9 @@
     <t>AMUS 228</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>A student in this cohort should be able to take all three courses. AMUS 228 and BHAV 212 each have one section and meet at the same time</t>
   </si>
   <si>
@@ -523,13 +538,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-06</t>
+    <t>2026-10-07</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>13:27:37</t>
+    <t>08:51:36</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -545,9 +560,6 @@
   </si>
   <si>
     <t>Time Stamp In File Name</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>Default Department</t>
@@ -937,7 +949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -958,9 +970,10 @@
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,719 +1037,755 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2">
         <v>65</v>
       </c>
       <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
         <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
       </c>
       <c r="L3">
         <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4">
         <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5">
         <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8">
         <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="V11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" t="s">
+        <v>38</v>
+      </c>
+      <c r="V12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1778,13 +1827,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1808,22 +1857,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -1832,10 +1881,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -1844,10 +1893,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -1858,31 +1907,31 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1891,78 +1940,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
         <v>36</v>
       </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" t="s">
-        <v>35</v>
-      </c>
       <c r="W2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1971,78 +2020,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -2051,78 +2100,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2131,78 +2180,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -2211,78 +2260,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2291,78 +2340,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2371,78 +2420,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2451,78 +2500,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -2531,78 +2580,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O10">
         <v>65</v>
       </c>
       <c r="P10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2611,78 +2660,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O11">
         <v>65</v>
       </c>
       <c r="P11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
         <v>71</v>
-      </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
-        <v>70</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -2691,49 +2740,49 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2754,7 +2803,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2781,19 +2830,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -2807,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2825,255 +2874,293 @@
     <col min="17" max="17" width="4" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="23" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>137</v>
+      </c>
+      <c r="W2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" t="s">
+        <v>137</v>
+      </c>
+      <c r="W3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>134</v>
       </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>130</v>
-      </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" t="s">
+        <v>137</v>
+      </c>
+      <c r="W4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3095,122 +3182,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3218,19 +3305,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3238,19 +3325,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,19 +3345,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3278,33 +3365,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3315,16 +3402,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3335,16 +3422,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -3355,16 +3442,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3375,16 +3462,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -3395,16 +3482,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -3415,16 +3502,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -3435,16 +3522,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" t="s">
         <v>152</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" t="s">
-        <v>147</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3470,90 +3557,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -544,7 +544,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:51:36</t>
+    <t>12:17:43</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -544,7 +544,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>12:17:43</t>
+    <t>14:23:18</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-with-conflicts.xlsx
+++ b/apps/web/public/examples/example-with-conflicts.xlsx
@@ -544,7 +544,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>14:23:18</t>
+    <t>15:09:00</t>
   </si>
   <si>
     <t>Academic Year</t>
